--- a/pacjenci/KRZYSZTOF OSAK.xlsx
+++ b/pacjenci/KRZYSZTOF OSAK.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/KRZYSZTOF OSAK.xlsx
+++ b/pacjenci/KRZYSZTOF OSAK.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>27.21.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania klinicznego przed rozpoczęciem leczenia.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 84mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywny metabolicznie węzeł chłonny nadobojczykowy po stronie lewej średnicy wg PET 11mm, SUV max 5,0 oraz grupy 5 po stronie prawej średnicy wg PET do 11mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Duża heterogenna metabolicznie masa miękkotkankowa obejmująca śródpiersie przednie obustronnie, węzły chłonne położone lewobocznie od łuku aorty, przytchawicze prawe, przymostkowe obustronnie, wnęki płuca prawego położone prawobocznie od serca o łącznej wielkości w TK do 184x94x168mm, SUV max do 11,0. Aktywne metabolicznie węzły chłonne: - do przodu od 1. żebra prawego średnicy wg PET 12mm, SUV max 3,4, - przytchawicze górne obustronnie  średnicy wg PET 13mm, SUV max 6,7, - okna aortalno-płucnego średnicy wg PET 15mm, SUV max 7,2, - podostrogowe wielkości wg PET 56x19mm, SUV max 18,4, - położony pomiędzy prawy przedsionkiem a żyłą główną górną średnicy wg PET 15mm, SUV max 6,0 - przedsercowo w tkance tłuszczowej po stronie prawej w zachyłku przeponowo-żebrowym wielkości 56x21mm, SUV max 11,4. Aktywny metabolicznie obszar w segmencie 9 płuca lewego w topografii guza/zagęszczeń miąższowych średnicy wg PET 13mm, SUV max 2,6 - naciek chłoniakowy? zmiany zapalno-niedodmowe? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w prawej jamie opłucnowej grubości płaszcza do 37mm, w lewej ślad.  Brzuch i miednica: Mierna rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z obecnością osteofitów przednich i cechami dyskopatii wielopoziomowo - najbardziej nasilonej w odcinku szyjnym. Ciasna dyskopatia L5/S1.   Wartości referencyjne: MBPS SUVmax 2,2, Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z obecnością aktywnych metabolicznie zmian chłoniakowych po jednej stronie przepony i pojedynczej aktywnej metabolicznie zmiany w płucach - zmiana niedodmowo-zapalna? naciek chłoniakowy?</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>18.4</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>05.04.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Wczesna ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 109mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w migdałku gardłowym lewym-do kontroli.  Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Rozległa niejednorodna metabolicznie masa miękkotkankowa obejmująca: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x101x156mm, SUV max do 3,3. Masa w znacznym stopniu uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 24x12mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, wielkości do 15x12mm.Zwiększona ilość płynu w prawej jamie opłucnowej o szerokości płaszcza do 43mm. Niewielkie zmiany miąższowo-włókniste w segm. 9 i 10 płuca prawego, nadprzeponowo. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.    Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono częściową regresję metaboliczną i radiologiczną procesu chłoniakowego na stosowane leczenie. Masa miękkotkankowa w KLP do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>09.08.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena odpowiedzi po zakończeniu chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 112mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywność metaboliczna w fałdach głosowych - do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Mierne niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x91x112mm, SUV max do 3,3, masa prawdopodobnie uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 23x13mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, średnicy do 15mm. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Aktywny metabolicznie obszar w lewobocznej części rękojeści mostka wielkości wg PET 23x18mm, SUV max 8,4.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w lewobocznej części rękojeści mostka - konieczna weryfikacja/kontrola.  Masa miękkotkankowa w KLP do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>8.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>24.01.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena  remisji choroby 3 m-ce po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Mierne, niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 124x74 mm [Im fuz. 115] x116mm, SUV max do 3,0; masa prawdopodobnie uciska/nacieka płat górny prawego płuca - dokładna ocena możliwa jest w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 16x9 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Ok. 5mm uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem,. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w KLP - do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>4.8</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/KRZYSZTOF OSAK.xlsx
+++ b/pacjenci/KRZYSZTOF OSAK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 84mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie węzeł chłonny nadobojczykowy po stronie lewej średnicy wg PET 11mm, SUV max 5,0 oraz grupy 5 po stronie prawej średnicy wg PET do 11mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Duża heterogenna metabolicznie masa miękkotkankowa obejmująca śródpiersie przednie obustronnie, węzły chłonne położone lewobocznie od łuku aorty, przytchawicze prawe, przymostkowe obustronnie, wnęki płuca prawego położone prawobocznie od serca o łącznej wielkości w TK do 184x94x168mm, SUV max do 11,0. Aktywne metabolicznie węzły chłonne: - do przodu od 1. żebra prawego średnicy wg PET 12mm, SUV max 3,4, - przytchawicze górne obustronnie  średnicy wg PET 13mm, SUV max 6,7, - okna aortalno-płucnego średnicy wg PET 15mm, SUV max 7,2, - podostrogowe wielkości wg PET 56x19mm, SUV max 18,4, - położony pomiędzy prawy przedsionkiem a żyłą główną górną średnicy wg PET 15mm, SUV max 6,0 - przedsercowo w tkance tłuszczowej po stronie prawej w zachyłku przeponowo-żebrowym wielkości 56x21mm, SUV max 11,4. Aktywny metabolicznie obszar w segmencie 9 płuca lewego w topografii guza/zagęszczeń miąższowych średnicy wg PET 13mm, SUV max 2,6 - naciek chłoniakowy? zmiany zapalno-niedodmowe? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w prawej jamie opłucnowej grubości płaszcza do 37mm, w lewej ślad.  Brzuch i miednica: Mierna rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z obecnością osteofitów przednich i cechami dyskopatii wielopoziomowo - najbardziej nasilonej w odcinku szyjnym. Ciasna dyskopatia L5/S1.   Wartości referencyjne: MBPS SUVmax 2,2, Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny nadobojczykowy po stronie lewej średnicy wg PET 11mm, SUV max 5,0 oraz grupy 5 po stronie prawej średnicy wg PET do 11mm, SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Duża heterogenna metabolicznie masa miękkotkankowa obejmująca śródpiersie przednie obustronnie, węzły chłonne położone lewobocznie od łuku aorty, przytchawicze prawe, przymostkowe obustronnie, wnęki płuca prawego położone prawobocznie od serca o łącznej wielkości w TK do 184x94x168mm, SUV max do 11,0. Aktywne metabolicznie węzły chłonne: - do przodu od 1. żebra prawego średnicy wg PET 12mm, SUV max 3,4, - przytchawicze górne obustronnie  średnicy wg PET 13mm, SUV max 6,7, - okna aortalno-płucnego średnicy wg PET 15mm, SUV max 7,2, - podostrogowe wielkości wg PET 56x19mm, SUV max 18,4, - położony pomiędzy prawy przedsionkiem a żyłą główną górną średnicy wg PET 15mm, SUV max 6,0 - przedsercowo w tkance tłuszczowej po stronie prawej w zachyłku przeponowo-żebrowym wielkości 56x21mm, SUV max 11,4. Aktywny metabolicznie obszar w segmencie 9 płuca lewego w topografii guza/zagęszczeń miąższowych średnicy wg PET 13mm, SUV max 2,6 - naciek chłoniakowy? zmiany zapalno-niedodmowe? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w prawej jamie opłucnowej grubości płaszcza do 37mm, w lewej ślad.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Mierna rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z obecnością osteofitów przednich i cechami dyskopatii wielopoziomowo - najbardziej nasilonej w odcinku szyjnym. Ciasna dyskopatia L5/S1.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z obecnością aktywnych metabolicznie zmian chłoniakowych po jednej stronie przepony i pojedynczej aktywnej metabolicznie zmiany w płucach - zmiana niedodmowo-zapalna? naciek chłoniakowy?</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>18.4</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 109mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w migdałku gardłowym lewym-do kontroli.  Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Rozległa niejednorodna metabolicznie masa miękkotkankowa obejmująca: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x101x156mm, SUV max do 3,3. Masa w znacznym stopniu uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 24x12mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, wielkości do 15x12mm.Zwiększona ilość płynu w prawej jamie opłucnowej o szerokości płaszcza do 43mm. Niewielkie zmiany miąższowo-włókniste w segm. 9 i 10 płuca prawego, nadprzeponowo. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.    Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w migdałku gardłowym lewym-do kontroli.  Asymetryczne pobudzenie metaboliczne w fałdzie głosowym prawym- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rozległa niejednorodna metabolicznie masa miękkotkankowa obejmująca: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x101x156mm, SUV max do 3,3. Masa w znacznym stopniu uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 24x12mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, wielkości do 15x12mm.Zwiększona ilość płynu w prawej jamie opłucnowej o szerokości płaszcza do 43mm. Niewielkie zmiany miąższowo-włókniste w segm. 9 i 10 płuca prawego, nadprzeponowo. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 3,1 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono częściową regresję metaboliczną i radiologiczną procesu chłoniakowego na stosowane leczenie. Masa miękkotkankowa w KLP do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 112mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Aktywność metaboliczna w fałdach głosowych - do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Mierne niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x91x112mm, SUV max do 3,3, masa prawdopodobnie uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 23x13mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, średnicy do 15mm. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Aktywny metabolicznie obszar w lewobocznej części rękojeści mostka wielkości wg PET 23x18mm, SUV max 8,4.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w fałdach głosowych - do kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mierne niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 129x91x112mm, SUV max do 3,3, masa prawdopodobnie uciska/nacieka płat górny prawego płuca  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 23x13mm. Separujące się węzły chłonne położone lewobocznie od łuku aorty, średnicy do 15mm. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki lewej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w lewobocznej części rękojeści mostka wielkości wg PET 23x18mm, SUV max 8,4.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie obszar w lewobocznej części rękojeści mostka - konieczna weryfikacja/kontrola.  Masa miękkotkankowa w KLP do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>8.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Mierne, niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 124x74 mm [Im fuz. 115] x116mm, SUV max do 3,0; masa prawdopodobnie uciska/nacieka płat górny prawego płuca - dokładna ocena możliwa jest w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 16x9 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.  Brzuch i miednica: Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Ok. 5mm uwapniony konkrement w UKM-ie nerki lewej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem,. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca powiększona, zwłaszcza w zakresie lewego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mierne, niejednorodne pobudzenie metaboliczne w rozległej masie miękkotkankowej obejmującej: śródpiersie przednie pośrodkowo i po stronie prawej, węzły chłonne zamostkowe, zwłaszcza po stronie prawej, przytchawicze górne i dolne prawe, wnęki płuca prawego oraz zlokalizowane przysercowo po stronie prawej, o orientacyjnej wielkości ok.: 124x74 mm [Im fuz. 115] x116mm, SUV max do 3,0; masa prawdopodobnie uciska/nacieka płat górny prawego płuca - dokładna ocena możliwa jest w badaniu TK KLP z kontrastem dożylnym.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Separujący się od powyżej opisanej masy węzeł chłonny przytchawiczy dolny prawy, wielkości 16x9 mm. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca lewego. Drobny podopłucnowy guzek średnicy 5 mm w segmencie 10 płuca prawego.  Niewielkie zmiany włókniste nadprzeponowo obustronnie.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Miernie rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka, SUV max 4,8 - w pierwszej kolejności czynnościowo. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Ok. 5mm uwapniony konkrement w UKM-ie nerki lewej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem,. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa lędźwiowego. Zniesienie fizjologicznej lordozy oraz wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Ciasna dyskopatia na poziomie L5/S1. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masa miękkotkankowa w KLP - do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>4.8</v>
       </c>
     </row>
